--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZM\Desktop\electronic-component-price-scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BEBC87-DA56-4977-8884-9C7C0A6D1A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA1896A-9BE3-465D-899B-4D0074189233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4038D84F-0F22-477E-BAD2-EF11977D4FC7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="180">
   <si>
     <t>https://lionelectronic.ir/products/2867-SMBJ16A</t>
   </si>
@@ -583,6 +583,9 @@
   </si>
   <si>
     <t>CH49</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -822,7 +825,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1275,7 +1278,9 @@
       <c r="F1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="26" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12">

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZM\Desktop\electronic-component-price-scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B1C029-C459-4EA1-A65D-960C09851168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D376BFE-DB39-4ABC-B2ED-C748EFDBE775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4038D84F-0F22-477E-BAD2-EF11977D4FC7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>https://www.javanelec.com/shop/product/11930/non-brand/led-smd-1206-red/%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-%d8%a7%d8%b3-%d8%a7%d9%85-%d8%af%db%8c-1206-%d9%82%d8%b1%d9%85%d8%b2</t>
   </si>
@@ -175,6 +175,12 @@
   </si>
   <si>
     <t>https://www.generalelec.com/product/10749/MARR-5-32-38</t>
+  </si>
+  <si>
+    <t>https://lionelectronic.ir/products/6784-B_4500mAH_3C_T1</t>
+  </si>
+  <si>
+    <t>https://lionelectronic.ir/products/6723-DRV8411RTER</t>
   </si>
 </sst>
 </file>
@@ -635,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77EC03A-ACDF-4A4F-8E12-C1C948D4BE5F}">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="23.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="4"/>
@@ -667,485 +673,491 @@
       </c>
     </row>
     <row r="3" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12">
-        <v>3</v>
-      </c>
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
       <c r="C3" s="9" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12">
-        <v>1</v>
-      </c>
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="9" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8">
         <v>2</v>
       </c>
+      <c r="B5" s="12">
+        <v>3</v>
+      </c>
       <c r="C5" s="9" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" s="11">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>5</v>
-      </c>
-      <c r="B6" s="8">
-        <v>2</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="8">
         <v>1</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="8">
         <v>1</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="8">
         <v>1</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A12" s="11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A16" s="11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A18" s="11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="8">
         <v>1</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="11">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="8">
         <v>1</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A22" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="8">
         <v>1</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A23" s="11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="8">
         <v>1</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A24" s="11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="8">
         <v>1</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="8">
         <v>1</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A26" s="11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="8">
         <v>1</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="8">
         <v>1</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A28" s="11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="8">
         <v>1</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="8">
         <v>1</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A30" s="11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="8">
         <v>1</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11">
-        <v>30</v>
-      </c>
-      <c r="B31" s="12">
+        <v>28</v>
+      </c>
+      <c r="B31" s="8">
         <v>1</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A32" s="11">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="8">
         <v>1</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C32" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="11">
-        <v>32</v>
-      </c>
-      <c r="B33" s="8">
+        <v>30</v>
+      </c>
+      <c r="B33" s="12">
         <v>1</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>13</v>
+      <c r="C33" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="11">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8">
         <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8">
         <v>1</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="11">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" s="8">
         <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="8">
         <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" s="11">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="8">
         <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" s="8">
         <v>1</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" s="8">
         <v>1</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" s="8">
         <v>1</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" s="11">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" s="8">
         <v>1</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" s="8">
         <v>1</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" s="11">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="8">
         <v>1</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45" s="8">
         <v>1</v>
       </c>
       <c r="C45" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="11">
+        <v>43</v>
+      </c>
+      <c r="B46" s="8">
+        <v>1</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" s="11">
+        <v>44</v>
+      </c>
+      <c r="B47" s="8">
+        <v>1</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" s="3"/>
@@ -4731,13 +4743,21 @@
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
     </row>
+    <row r="944" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A944" s="3"/>
+      <c r="B944" s="3"/>
+    </row>
+    <row r="945" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A945" s="3"/>
+      <c r="B945" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{25CDF3FE-77E6-473B-865D-EA3763CDFE34}"/>
-    <hyperlink ref="C31" r:id="rId2" xr:uid="{EEAEAFE3-A45A-4379-BD6C-F4257BE07EB6}"/>
-    <hyperlink ref="C34" r:id="rId3" xr:uid="{448E77A0-A160-4496-9C90-13AD5F396A6B}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{25CDF3FE-77E6-473B-865D-EA3763CDFE34}"/>
+    <hyperlink ref="C33" r:id="rId2" xr:uid="{EEAEAFE3-A45A-4379-BD6C-F4257BE07EB6}"/>
+    <hyperlink ref="C36" r:id="rId3" xr:uid="{448E77A0-A160-4496-9C90-13AD5F396A6B}"/>
     <hyperlink ref="C2" r:id="rId4" xr:uid="{5F566020-6F70-4436-ABAD-82C018177E41}"/>
-    <hyperlink ref="C19" r:id="rId5" xr:uid="{00D6EE1E-140B-4CBA-B869-2AA5395C747B}"/>
+    <hyperlink ref="C21" r:id="rId5" xr:uid="{00D6EE1E-140B-4CBA-B869-2AA5395C747B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZM\Desktop\electronic-component-price-scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D376BFE-DB39-4ABC-B2ED-C748EFDBE775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB80248-5C55-4913-9DD6-7E1901EAC493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4038D84F-0F22-477E-BAD2-EF11977D4FC7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>https://www.javanelec.com/shop/product/11930/non-brand/led-smd-1206-red/%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-%d8%a7%d8%b3-%d8%a7%d9%85-%d8%af%db%8c-1206-%d9%82%d8%b1%d9%85%d8%b2</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>https://lionelectronic.ir/products/6723-DRV8411RTER</t>
+  </si>
+  <si>
+    <t>https://buybestelectronic.com/parts/stm32f407zgt6</t>
   </si>
 </sst>
 </file>
@@ -641,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77EC03A-ACDF-4A4F-8E12-C1C948D4BE5F}">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="23.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="4"/>
@@ -661,507 +664,518 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11">
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12">
         <v>3</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
     <row r="4" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11"/>
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
       <c r="B4" s="12"/>
       <c r="C4" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" s="11">
-        <v>2</v>
-      </c>
-      <c r="B5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="11">
-        <v>3</v>
-      </c>
-      <c r="B6" s="12">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="11">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="12">
+        <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
         <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="11">
-        <v>5</v>
       </c>
       <c r="B8" s="8">
         <v>2</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
         <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11">
-        <v>7</v>
       </c>
       <c r="B10" s="8">
         <v>1</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="8">
         <v>1</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
         <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="11">
-        <v>9</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="11">
-        <v>11</v>
+      <c r="A14" s="1">
+        <v>13</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="8">
         <v>1</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="11">
-        <v>13</v>
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="8">
+        <v>1</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8">
         <v>2</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="11">
-        <v>15</v>
-      </c>
-      <c r="B18" s="8">
-        <v>1</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="8">
         <v>1</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="11">
-        <v>17</v>
+      <c r="A20" s="1">
+        <v>19</v>
       </c>
       <c r="B20" s="8">
         <v>1</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="8">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8">
         <v>10</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="11">
-        <v>19</v>
-      </c>
-      <c r="B22" s="8">
-        <v>1</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A23" s="11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="8">
         <v>1</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="11">
-        <v>21</v>
+      <c r="A24" s="1">
+        <v>23</v>
       </c>
       <c r="B24" s="8">
         <v>1</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="8">
         <v>1</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="11">
-        <v>23</v>
+      <c r="A26" s="1">
+        <v>25</v>
       </c>
       <c r="B26" s="8">
         <v>1</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" s="8">
         <v>1</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="11">
-        <v>25</v>
+      <c r="A28" s="1">
+        <v>27</v>
       </c>
       <c r="B28" s="8">
         <v>1</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8">
         <v>1</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="11">
-        <v>27</v>
+      <c r="A30" s="1">
+        <v>29</v>
       </c>
       <c r="B30" s="8">
         <v>1</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="8">
         <v>1</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="11">
-        <v>29</v>
+      <c r="A32" s="1">
+        <v>31</v>
       </c>
       <c r="B32" s="8">
         <v>1</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="11">
-        <v>30</v>
-      </c>
-      <c r="B33" s="12">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8">
         <v>1</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="12">
+        <v>1</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" s="11">
-        <v>31</v>
-      </c>
-      <c r="B34" s="8">
-        <v>1</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" s="8">
         <v>1</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" s="11">
-        <v>33</v>
+      <c r="A36" s="1">
+        <v>35</v>
       </c>
       <c r="B36" s="8">
         <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="8">
         <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" s="11">
-        <v>35</v>
+      <c r="A38" s="1">
+        <v>37</v>
       </c>
       <c r="B38" s="8">
         <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="8">
         <v>1</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" s="11">
-        <v>37</v>
+      <c r="A40" s="1">
+        <v>39</v>
       </c>
       <c r="B40" s="8">
         <v>1</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="8">
         <v>1</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A42" s="11">
-        <v>39</v>
+      <c r="A42" s="1">
+        <v>41</v>
       </c>
       <c r="B42" s="8">
         <v>1</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43" s="8">
         <v>1</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44" s="11">
-        <v>41</v>
+      <c r="A44" s="1">
+        <v>43</v>
       </c>
       <c r="B44" s="8">
         <v>1</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="8">
         <v>1</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46" s="11">
-        <v>43</v>
+      <c r="A46" s="1">
+        <v>45</v>
       </c>
       <c r="B46" s="8">
         <v>1</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" s="11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B47" s="8">
         <v>1</v>
       </c>
       <c r="C47" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8">
+        <v>1</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" s="3"/>
@@ -4751,13 +4765,17 @@
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
     </row>
+    <row r="946" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A946" s="3"/>
+      <c r="B946" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{25CDF3FE-77E6-473B-865D-EA3763CDFE34}"/>
-    <hyperlink ref="C33" r:id="rId2" xr:uid="{EEAEAFE3-A45A-4379-BD6C-F4257BE07EB6}"/>
-    <hyperlink ref="C36" r:id="rId3" xr:uid="{448E77A0-A160-4496-9C90-13AD5F396A6B}"/>
-    <hyperlink ref="C2" r:id="rId4" xr:uid="{5F566020-6F70-4436-ABAD-82C018177E41}"/>
-    <hyperlink ref="C21" r:id="rId5" xr:uid="{00D6EE1E-140B-4CBA-B869-2AA5395C747B}"/>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{25CDF3FE-77E6-473B-865D-EA3763CDFE34}"/>
+    <hyperlink ref="C34" r:id="rId2" xr:uid="{EEAEAFE3-A45A-4379-BD6C-F4257BE07EB6}"/>
+    <hyperlink ref="C37" r:id="rId3" xr:uid="{448E77A0-A160-4496-9C90-13AD5F396A6B}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{5F566020-6F70-4436-ABAD-82C018177E41}"/>
+    <hyperlink ref="C22" r:id="rId5" xr:uid="{00D6EE1E-140B-4CBA-B869-2AA5395C747B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZM\Desktop\electronic-component-price-scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D61B671-BF5F-4FA8-9F7B-4F44FCFA6F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F552D49-773B-4BD1-BBDF-ED04ABF01741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3624" yWindow="3624" windowWidth="17280" windowHeight="9960" xr2:uid="{4038D84F-0F22-477E-BAD2-EF11977D4FC7}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{4038D84F-0F22-477E-BAD2-EF11977D4FC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>https://www.javanelec.com/shop/product/11930/non-brand/led-smd-1206-red/%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-%d8%a7%d8%b3-%d8%a7%d9%85-%d8%af%db%8c-1206-%d9%82%d8%b1%d9%85%d8%b2</t>
   </si>
@@ -94,6 +94,78 @@
   </si>
   <si>
     <t>https://shop.ideaelec.com/product/esp8266-12e/</t>
+  </si>
+  <si>
+    <t>https://arefelectronic.com/%d8%b1%d9%84%d9%87-%d8%a7%d9%85%d8%b1%d9%86-%d9%85%d8%af%d9%84-g2r-1-e-%d8%af%d8%a7%d8%b1%d8%a7%db%8c-12-%d9%88%d9%84%d8%aa-%d9%88-8-%d9%be%db%8c%d9%86/</t>
+  </si>
+  <si>
+    <t>https://ariaebox.com/product/%d8%a8%d8%a7%da%a9%d8%b3-%d8%b4%d9%81%d8%a7%d9%81-%d8%a8%d8%b1%d8%af-%da%a9%d9%86%d8%aa%d8%b1%d9%84-%d8%b5%d9%86%d8%b9%d8%aa%db%8c-%d8%b1%db%8c%d9%84%db%8c-abr113-a2t-%d8%a8%d8%a7-%d8%a7%d8%a8%d8%b9/</t>
+  </si>
+  <si>
+    <t>https://efarvahar.ir/usb-connector/493-male-3.html</t>
+  </si>
+  <si>
+    <t>https://www.iran-module.ir/product_info.php/products_id/2658/pname/%D9%85%D8%A7%DA%98%D9%88%D9%84-%D8%B1%DA%AF%D9%88%D9%84%D8%A7%D8%AA%D9%88%D8%B1-DC-%D8%A8%D9%87-DC-%D8%A7%D9%81%D8%B2%D8%A7%DB%8C%D9%86%D8%AF%D9%87-100-%D9%88%D8%A7%D8%AA-LTC1871-%D9%87%D9%85%D8%B1%D8%A7%D9%87-%D8%A8%D8%A7-%D9%86%D9%85%D8%A7%DB%8C%D8%B4%DA%AF%D8%B1-%D9%88%D9%84%D8%AA%D8%A7%DA%98</t>
+  </si>
+  <si>
+    <t>https://nemonehsaz.com/%D9%87%DB%8C%D8%AA-%D8%A8%D8%AF-%D9%BE%D8%B1%DB%8C%D9%86%D8%AA%D8%B1-%D8%B3%D9%87-%D8%A8%D8%B9%D8%AF%DB%8C-214x214-PCB-Heat-Bed</t>
+  </si>
+  <si>
+    <t>https://elecohm.com/product/%da%a9%d8%a7%d8%a8%d9%84-usb-%d9%be%d8%b1%d9%8a%d9%86%d8%aa%d8%b1-30-%d8%b3%d8%a7%d9%86%d8%aa%db%8c%d9%85%d8%aa%d8%b1-%d9%85%d9%86%d8%a7%d8%b3%d8%a8-%d8%a8%d8%b1%d8%a7%db%8c-%d9%be%d8%b1/</t>
+  </si>
+  <si>
+    <t>https://avaelectronic.ir/product/%d9%87%db%8c%d8%aa-%d8%b3%db%8c%d9%86%da%a9-%d9%85%d9%86%d8%a7%d8%b3%d8%a8-%d8%b1%d8%b2%d8%a8%d8%b1%db%8c-%d9%be%d8%a7%db%8c-raspberry-pi-4/</t>
+  </si>
+  <si>
+    <t>https://sepehrelec.com/Products/%d8%a8%d9%84%d9%86%d8%af%da%af%d9%88%db%8c-8-%d8%a7%d9%87%d9%85-YD50-%d9%86%db%8c%d9%85-%d9%88%d8%a7%d8%aa-P103006021.aspx</t>
+  </si>
+  <si>
+    <t>https://www.generalelec.com/product/10749/MARR-5-32-38</t>
+  </si>
+  <si>
+    <t>https://irenx.ir/shop/product/rain-sensor-module/</t>
+  </si>
+  <si>
+    <t>https://landaelectronic.com/product/dc-gear-motor-zga12-fn20-6v_70rpm/</t>
+  </si>
+  <si>
+    <t>https://nikushop.com/product/h21a1/</t>
+  </si>
+  <si>
+    <t>https://www.denizetc.com/terminal-block-kf129r-2pin-5-0mm</t>
+  </si>
+  <si>
+    <t>https://skytech.ir/product_details.aspx?ID_Parts=22724&amp;3MM-YELLOW-LED</t>
+  </si>
+  <si>
+    <t>https://daneshjookit.com/%D9%85%DA%A9%D8%A7%D9%86%DB%8C%DA%A9-%D8%B1%D8%A8%D8%A7%D8%AA%DB%8C%DA%A9-robotic/%D9%82%D8%B7%D8%B9%D8%A7%D8%AA-%D9%85%DA%A9%D8%A7%D9%86%DB%8C%DA%A9%DB%8C-%D8%B1%D8%A8%D8%A7%D8%AA%DB%8C%DA%A9/%D9%BE%DB%8C%DA%86-%D9%88-%D9%85%D9%87%D8%B1%D9%87/5874-spacer-45mm-f-f.html</t>
+  </si>
+  <si>
+    <t>https://www.alphakit.ir/product/%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-50-%d9%88%d8%a7%d8%aa-12-24-%d9%88%d9%84%d8%aa-cob-%d9%85%d9%87%d8%aa%d8%a7%d8%a8%db%8c-%da%a9%d9%84%db%8c%d8%af%d8%af%d8%a7%d8%b1/</t>
+  </si>
+  <si>
+    <t>https://bazaarbargh.ir/product/%d9%85%d8%a7%da%98%d9%88%d9%84-%d8%a7%d9%84-%d8%a7%db%8c-%d8%af%db%8c-rgb-ws2812-%d9%85%d8%b1%d8%a8%d8%b9%db%8c-4x4/</t>
+  </si>
+  <si>
+    <t>https://www.merqc.com/item/3571/%D8%AF%D9%85_%DA%AF%D8%B1%D8%AF_%D9%BE%D8%B1%D9%88%D8%B3%DA%A9%DB%8C%D8%AA_1PK_5</t>
+  </si>
+  <si>
+    <t>https://shop.rngo.ir/Arduino-boards/%D8%A8%D8%B1%D8%AF-%D8%A2%D8%B1%D8%AF%D9%88%DB%8C%D9%86%D9%88-mega2560-r3</t>
+  </si>
+  <si>
+    <t>https://iecshop.ir/QC-PASS-LABEL-HOLOGRAM-120PCS</t>
+  </si>
+  <si>
+    <t>https://sparkeyelec.ir/product/%d9%85%d8%a7%da%98%d9%88%d9%84-%d8%a8%d9%84%d9%88%d8%aa%d9%88%d8%ab-hc-05/</t>
+  </si>
+  <si>
+    <t>https://donya-ic.ir/shop/10uf-450v/</t>
+  </si>
+  <si>
+    <t>https://rizsmd.com/product/zener-2-4v-minimelf-smd/</t>
+  </si>
+  <si>
+    <t>https://iran-micro.com/%D8%A2%D9%85%D9%BE%D8%B1-%D9%85%D8%AA%D8%B1-%D8%B9%D9%82%D8%B1%D8%A8%D9%87-%D8%A7%DB%8C-%D8%A2%D9%86%D8%A7%D9%84%D9%88%DA%AF-500-%D9%85%DB%8C%D9%84%DB%8C-%D8%A2%D9%85%D9%BE%D8%B1-500ma-dc</t>
   </si>
 </sst>
 </file>
@@ -188,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -205,6 +277,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77EC03A-ACDF-4A4F-8E12-C1C948D4BE5F}">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="23.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
@@ -563,22 +637,22 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
-        <v>3</v>
+      <c r="B2" s="1">
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -589,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -600,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -611,18 +685,18 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -633,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -641,10 +715,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
@@ -663,10 +737,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -677,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -688,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -699,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -710,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -721,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -750,137 +824,288 @@
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="1"/>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="4"/>
-      <c r="B28" s="1"/>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="4">
+        <v>45</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="4"/>
-      <c r="B29" s="1"/>
+      <c r="A29" s="4">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="4"/>
-      <c r="B30" s="1"/>
+      <c r="A30" s="4">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="4"/>
-      <c r="B31" s="1"/>
+      <c r="A31" s="4">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="4"/>
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="4">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" s="4"/>
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" s="4"/>
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" s="4"/>
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" s="4"/>
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" s="4"/>
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" s="4"/>
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" s="4"/>
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" s="4"/>
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" s="4"/>
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" s="4"/>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B33" s="1"/>
+      <c r="C33" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" s="4">
+        <v>40</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="4">
+        <v>42</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="4">
+        <v>43</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="4">
+        <v>44</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="4">
+        <v>46</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="4">
+        <v>47</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="4">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A44" s="4"/>
       <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" s="4"/>
+      <c r="C44" s="8"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" s="1"/>
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="4"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="1"/>
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
     </row>
@@ -4404,81 +4629,19 @@
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
     </row>
-    <row r="929" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A929" s="1"/>
-      <c r="B929" s="1"/>
-    </row>
-    <row r="930" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A930" s="1"/>
-      <c r="B930" s="1"/>
-    </row>
-    <row r="931" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A931" s="1"/>
-      <c r="B931" s="1"/>
-    </row>
-    <row r="932" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A932" s="1"/>
-      <c r="B932" s="1"/>
-    </row>
-    <row r="933" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A933" s="1"/>
-      <c r="B933" s="1"/>
-    </row>
-    <row r="934" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A934" s="1"/>
-      <c r="B934" s="1"/>
-    </row>
-    <row r="935" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A935" s="1"/>
-      <c r="B935" s="1"/>
-    </row>
-    <row r="936" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A936" s="1"/>
-      <c r="B936" s="1"/>
-    </row>
-    <row r="937" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A937" s="1"/>
-      <c r="B937" s="1"/>
-    </row>
-    <row r="938" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A938" s="1"/>
-      <c r="B938" s="1"/>
-    </row>
-    <row r="939" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A939" s="1"/>
-      <c r="B939" s="1"/>
-    </row>
-    <row r="940" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A940" s="1"/>
-      <c r="B940" s="1"/>
-    </row>
-    <row r="941" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A941" s="1"/>
-      <c r="B941" s="1"/>
-    </row>
-    <row r="942" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A942" s="1"/>
-      <c r="B942" s="1"/>
-    </row>
-    <row r="943" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A943" s="1"/>
-      <c r="B943" s="1"/>
-    </row>
-    <row r="944" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A944" s="1"/>
-      <c r="B944" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{448E77A0-A160-4496-9C90-13AD5F396A6B}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{5F566020-6F70-4436-ABAD-82C018177E41}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{0C72CB8E-7F94-40F7-A5D8-2E8F3290CD5F}"/>
-    <hyperlink ref="C10" r:id="rId4" xr:uid="{648569D7-7556-461E-ACB7-5E85ED8C0E04}"/>
-    <hyperlink ref="C12" r:id="rId5" xr:uid="{9F74AB5D-E997-4D04-AF23-7379BAC2D582}"/>
-    <hyperlink ref="C15" r:id="rId6" xr:uid="{2DCAA518-C5D3-4CEE-8B0C-3E3B806A7AC4}"/>
-    <hyperlink ref="C18" r:id="rId7" xr:uid="{30D5AE55-FA0C-452F-95D7-3B5D4442DD29}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{448E77A0-A160-4496-9C90-13AD5F396A6B}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{0C72CB8E-7F94-40F7-A5D8-2E8F3290CD5F}"/>
+    <hyperlink ref="C10" r:id="rId3" xr:uid="{648569D7-7556-461E-ACB7-5E85ED8C0E04}"/>
+    <hyperlink ref="C11" r:id="rId4" xr:uid="{9F74AB5D-E997-4D04-AF23-7379BAC2D582}"/>
+    <hyperlink ref="C16" r:id="rId5" xr:uid="{2DCAA518-C5D3-4CEE-8B0C-3E3B806A7AC4}"/>
+    <hyperlink ref="C18" r:id="rId6" xr:uid="{30D5AE55-FA0C-452F-95D7-3B5D4442DD29}"/>
+    <hyperlink ref="C19" r:id="rId7" xr:uid="{F00ADB73-BCC8-45D8-BE56-62E0DCD667F5}"/>
+    <hyperlink ref="C31" r:id="rId8" xr:uid="{A2500DDE-408A-4706-9737-18B338829838}"/>
+    <hyperlink ref="C28" r:id="rId9" xr:uid="{36682A83-7D9B-4465-99CA-7476904E75A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>